--- a/e_commerce_forms/010_customer_service_survey--e_commerce_forms.xlsx
+++ b/e_commerce_forms/010_customer_service_survey--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,25 +520,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>customer_service_survey</t>
+          <t>customer_service_survey_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Have you had a positive experience with our customer service?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer Service Survey</t>
+          <t>Please provide any feedback about our customer service.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Customer Service Feedback</t>
+          <t>Did we fulfill your order correctly?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was the shipment delivered on time?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,24 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>E-commerce Forms</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Learn more about customer service interactions with this survey.</t>
-        </is>
-      </c>
+          <t>Was order tracking information provided?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was the order status communicated clearly?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was the return process easy?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -690,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was the product of good quality?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was the product description accurate?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was the delivery experience convenient?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -759,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Customer Service Interaction</t>
+          <t>Was customer support helpful?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>E-commerce Forms</t>
+          <t>Was communication clear and timely?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -805,20 +801,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>E-commerce Forms</t>
+          <t>Was the order total accurate?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -828,20 +824,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecommerce Forms</t>
+          <t>Was payment processing smooth?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -851,13 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>E-commerce Forms</t>
+          <t>Were shipping options clear and convenient?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -874,20 +870,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecommerce Forms</t>
+          <t>Was the payment method secure?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -897,20 +893,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>E-commerce Forms</t>
+          <t>Was the order completed successfully?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -920,174 +916,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>E-commerce Forms</t>
+          <t>Overall, how would you rate your experience with our customer service?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>E-commerce Forms</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>E-commerce Forms</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ecommerce Forms</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>E-commerce Forms</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>E-commerce Forms</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>E-commerce Forms</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_service_survey_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ecommerce Forms</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_service_survey_choices</t>
+          <t>customer_service_survey_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1147,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_service_survey_choices</t>
+          <t>customer_service_survey_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1164,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_4_choices</t>
+          <t>customer_service_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1181,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_4_choices</t>
+          <t>customer_service_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,177 +1033,177 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_9_choices</t>
+          <t>customer_service_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_9_choices</t>
+          <t>customer_service_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_10_choices</t>
+          <t>customer_service_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_10_choices</t>
+          <t>customer_service_survey_page_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_11_choices</t>
+          <t>customer_service_survey_page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_11_choices</t>
+          <t>customer_service_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_16_choices</t>
+          <t>customer_service_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_16_choices</t>
+          <t>customer_service_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_17_choices</t>
+          <t>customer_service_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_17_choices</t>
+          <t>customer_service_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no_issue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No issue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_23_choices</t>
+          <t>customer_service_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1220,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_23_choices</t>
+          <t>customer_service_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1237,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_24_choices</t>
+          <t>customer_service_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_24_choices</t>
+          <t>customer_service_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,34 +1271,374 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_25_choices</t>
+          <t>customer_service_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>customer_service_survey_page_25_choices</t>
+          <t>customer_service_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>not_sure</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not sure</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_13_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_13_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_14_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_14_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>customer_service_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
